--- a/LAS_Lahan.xlsx
+++ b/LAS_Lahan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{DAC1167B-792E-4B6B-9A37-B96323839589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{518DB8AD-7A23-428A-A890-EF7D40DB0943}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{DAC1167B-792E-4B6B-9A37-B96323839589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{440D669C-020F-4788-B4E0-844BD1DCA6B0}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F47777B-1E1C-4CF1-9CA3-8605F22A3034}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -50,82 +50,91 @@
     <t>Hutan lahan kering primer</t>
   </si>
   <si>
-    <t>Hutan sekunder kerapatan tinggi</t>
-  </si>
-  <si>
-    <t>Hutan sekunder kerapatan rendah</t>
-  </si>
-  <si>
-    <t>Hutan rawa primer</t>
-  </si>
-  <si>
-    <t>Hutan rawa sekunder</t>
-  </si>
-  <si>
     <t>Hutan mangrove primer</t>
   </si>
   <si>
     <t>Hutan mangrove sekunder</t>
   </si>
   <si>
-    <t>Tanaman kayu industri</t>
-  </si>
-  <si>
     <t>Kebun campuran</t>
   </si>
   <si>
-    <t>Agroforestri kopi</t>
-  </si>
-  <si>
-    <t>Karet agroforestri</t>
-  </si>
-  <si>
     <t>Karet monokultur</t>
   </si>
   <si>
-    <t>Kelapa sawit skala besar</t>
-  </si>
-  <si>
-    <t>Kelapa sawit skala kecil</t>
-  </si>
-  <si>
-    <t>Kelapa</t>
-  </si>
-  <si>
-    <t>Teh</t>
-  </si>
-  <si>
-    <t>Sawah irigasi</t>
-  </si>
-  <si>
-    <t>Sawah tadah hujan</t>
-  </si>
-  <si>
-    <t>Tebu</t>
-  </si>
-  <si>
-    <t>Tanaman semusim lain</t>
-  </si>
-  <si>
     <t>Semak belukar</t>
   </si>
   <si>
-    <t>Rerumputan</t>
-  </si>
-  <si>
-    <t>Tambang</t>
-  </si>
-  <si>
     <t>Lahan terbuka</t>
   </si>
   <si>
-    <t>Pemukiman</t>
-  </si>
-  <si>
     <t>Tambak</t>
   </si>
   <si>
-    <t>Tubuh air</t>
+    <t>Hutan lahan kering sekunder</t>
+  </si>
+  <si>
+    <t>Hutan kerangas kerapatan tinggi</t>
+  </si>
+  <si>
+    <t>Hutan kerangas kerapatan rendah</t>
+  </si>
+  <si>
+    <t>Hutan Rawa</t>
+  </si>
+  <si>
+    <t>Hutan pantai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jati</t>
+  </si>
+  <si>
+    <t>Kelapa Sawit monokultur</t>
+  </si>
+  <si>
+    <t>Kelapa Monokultur</t>
+  </si>
+  <si>
+    <t>Karet Agroforestri</t>
+  </si>
+  <si>
+    <t>Durian Agroforestri</t>
+  </si>
+  <si>
+    <t>Sawah padi</t>
+  </si>
+  <si>
+    <t>Pertanian lahan kering lainnya</t>
+  </si>
+  <si>
+    <t>Rasau</t>
+  </si>
+  <si>
+    <t>Lada</t>
+  </si>
+  <si>
+    <t>Padang rumput</t>
+  </si>
+  <si>
+    <t>Permukiman</t>
+  </si>
+  <si>
+    <t>Badan air/sungai</t>
+  </si>
+  <si>
+    <t>Lahan terbuka pantai</t>
+  </si>
+  <si>
+    <t>Lamun</t>
+  </si>
+  <si>
+    <t>Terumbu karang</t>
+  </si>
+  <si>
+    <t>Makroalga</t>
+  </si>
+  <si>
+    <t>Substrat terbuka</t>
   </si>
 </sst>
 </file>
@@ -497,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293AF27B-1DAA-4A41-B5F1-046952DA074E}">
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -579,67 +588,67 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>281147</v>
+        <v>43334</v>
       </c>
       <c r="D2">
-        <v>275961.40519691119</v>
+        <v>42601.876102874558</v>
       </c>
       <c r="E2">
-        <v>270871.45570912655</v>
+        <v>41882.12137085601</v>
       </c>
       <c r="F2">
-        <v>265875.38741378515</v>
+        <v>41174.526828051014</v>
       </c>
       <c r="G2">
-        <v>260971.46872625817</v>
+        <v>40478.887029194491</v>
       </c>
       <c r="H2">
-        <v>256157.99999999991</v>
+        <v>39794.999999999993</v>
       </c>
       <c r="I2">
-        <v>253404.43412886368</v>
+        <v>39152.377930022209</v>
       </c>
       <c r="J2">
-        <v>250680.46766515044</v>
+        <v>38520.133121630606</v>
       </c>
       <c r="K2">
-        <v>247985.78243055596</v>
+        <v>37898.097999568978</v>
       </c>
       <c r="L2">
-        <v>245320.06366702792</v>
+        <v>37286.107694638602</v>
       </c>
       <c r="M2">
-        <v>242683.00000000006</v>
+        <v>36683.999999999993</v>
       </c>
       <c r="N2">
-        <v>241125.12683951354</v>
+        <v>36136.924235335835</v>
       </c>
       <c r="O2">
-        <v>239577.25425090134</v>
+        <v>35598.007120008791</v>
       </c>
       <c r="P2">
-        <v>238039.31803674327</v>
+        <v>35067.126982463837</v>
       </c>
       <c r="Q2">
-        <v>236511.25441172649</v>
+        <v>34544.163965657965</v>
       </c>
       <c r="R2">
-        <v>234993.00000000003</v>
+        <v>34029.000000000007</v>
       </c>
       <c r="S2">
-        <v>234148.75562838794</v>
+        <v>33584.540300164917</v>
       </c>
       <c r="T2">
-        <v>233307.54431971392</v>
+        <v>33145.88577899443</v>
       </c>
       <c r="U2">
-        <v>232469.35517728608</v>
+        <v>32712.960613867632</v>
       </c>
       <c r="V2">
-        <v>231634.17734356035</v>
+        <v>32285.689972498312</v>
       </c>
       <c r="W2">
-        <v>230801.99999999994</v>
+        <v>31863.999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -647,70 +656,70 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>268650</v>
+        <v>35802</v>
       </c>
       <c r="D3">
-        <v>267129.48541786231</v>
+        <v>33985.362784813515</v>
       </c>
       <c r="E3">
-        <v>265617.57669686177</v>
+        <v>32260.90396110238</v>
       </c>
       <c r="F3">
-        <v>264114.22512924718</v>
+        <v>30623.946284679394</v>
       </c>
       <c r="G3">
-        <v>262619.38228294521</v>
+        <v>29070.049840441068</v>
       </c>
       <c r="H3">
-        <v>261133.00000000006</v>
+        <v>27594.999999999996</v>
       </c>
       <c r="I3">
-        <v>260189.81113874738</v>
+        <v>26417.270924778251</v>
       </c>
       <c r="J3">
-        <v>259250.02899065622</v>
+        <v>25289.80623711304</v>
       </c>
       <c r="K3">
-        <v>258313.64125098562</v>
+        <v>24210.460699436924</v>
       </c>
       <c r="L3">
-        <v>257380.63565943827</v>
+        <v>23177.180630937546</v>
       </c>
       <c r="M3">
-        <v>256450.99999999997</v>
+        <v>22188.000000000004</v>
       </c>
       <c r="N3">
-        <v>255203.11457979825</v>
+        <v>21603.172368379535</v>
       </c>
       <c r="O3">
-        <v>253961.30134501183</v>
+        <v>21033.759526677353</v>
       </c>
       <c r="P3">
-        <v>252725.53074850838</v>
+        <v>20479.355174412118</v>
       </c>
       <c r="Q3">
-        <v>251495.77338693125</v>
+        <v>19939.563720303333</v>
       </c>
       <c r="R3">
-        <v>250271.99999999994</v>
+        <v>19414</v>
       </c>
       <c r="S3">
-        <v>248683.15416504233</v>
+        <v>19078.824746439397</v>
       </c>
       <c r="T3">
-        <v>247104.39508004973</v>
+        <v>18749.436164898958</v>
       </c>
       <c r="U3">
-        <v>245535.65870953017</v>
+        <v>18425.734350708768</v>
       </c>
       <c r="V3">
-        <v>243976.88142451935</v>
+        <v>18107.621124014677</v>
       </c>
       <c r="W3">
-        <v>242427.99999999997</v>
+        <v>17795</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -718,70 +727,70 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>182483</v>
+        <v>51767</v>
       </c>
       <c r="D4">
-        <v>187204.83533475158</v>
+        <v>49041.77888823612</v>
       </c>
       <c r="E4">
-        <v>192048.85042832184</v>
+        <v>46460.024272657138</v>
       </c>
       <c r="F4">
-        <v>197018.20674069543</v>
+        <v>44014.183505355431</v>
       </c>
       <c r="G4">
-        <v>202116.14753615367</v>
+        <v>41697.10153989782</v>
       </c>
       <c r="H4">
-        <v>207346</v>
+        <v>39501.999999999978</v>
       </c>
       <c r="I4">
-        <v>211010.93116647884</v>
+        <v>37595.184687081513</v>
       </c>
       <c r="J4">
-        <v>214740.64159301107</v>
+        <v>35780.413945009575</v>
       </c>
       <c r="K4">
-        <v>218536.27628132861</v>
+        <v>34053.244657051837</v>
       </c>
       <c r="L4">
-        <v>222399.00047156942</v>
+        <v>32409.448181768912</v>
       </c>
       <c r="M4">
-        <v>226330.00000000015</v>
+        <v>30845.000000000007</v>
       </c>
       <c r="N4">
-        <v>228860.95806921681</v>
+        <v>29573.150611013341</v>
       </c>
       <c r="O4">
-        <v>231420.2188325004</v>
+        <v>28353.744109634586</v>
       </c>
       <c r="P4">
-        <v>234008.09878758385</v>
+        <v>27184.618088518593</v>
       </c>
       <c r="Q4">
-        <v>236624.91797146809</v>
+        <v>26063.699304089416</v>
       </c>
       <c r="R4">
-        <v>239271.00000000012</v>
+        <v>24989</v>
       </c>
       <c r="S4">
-        <v>241436.64114649958</v>
+        <v>24120.951592842135</v>
       </c>
       <c r="T4">
-        <v>243621.88350491121</v>
+        <v>23283.056774750232</v>
       </c>
       <c r="U4">
-        <v>245826.90448574867</v>
+        <v>22474.268093847113</v>
       </c>
       <c r="V4">
-        <v>248051.88310526777</v>
+        <v>21693.574483822591</v>
       </c>
       <c r="W4">
-        <v>250296.99999999997</v>
+        <v>20940.000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -789,70 +798,70 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>34376</v>
+        <v>15244</v>
       </c>
       <c r="D5">
-        <v>34119.603714164594</v>
+        <v>15273.088772907869</v>
       </c>
       <c r="E5">
-        <v>33865.119781581168</v>
+        <v>15302.23305334062</v>
       </c>
       <c r="F5">
-        <v>33612.533938802233</v>
+        <v>15331.432947218338</v>
       </c>
       <c r="G5">
-        <v>33361.832028765421</v>
+        <v>15360.688560663226</v>
       </c>
       <c r="H5">
-        <v>33113</v>
+        <v>15389.999999999991</v>
       </c>
       <c r="I5">
-        <v>32957.75105257854</v>
+        <v>15377.981242655738</v>
       </c>
       <c r="J5">
-        <v>32803.22998350321</v>
+        <v>15365.971871310703</v>
       </c>
       <c r="K5">
-        <v>32649.433380146129</v>
+        <v>15353.971878634939</v>
       </c>
       <c r="L5">
-        <v>32496.357845879382</v>
+        <v>15341.981257304209</v>
       </c>
       <c r="M5">
-        <v>32344</v>
+        <v>15330.000000000002</v>
       </c>
       <c r="N5">
-        <v>32233.852333576491</v>
+        <v>15326.598490841807</v>
       </c>
       <c r="O5">
-        <v>32124.079775624989</v>
+        <v>15323.19773643016</v>
       </c>
       <c r="P5">
-        <v>32014.681048711569</v>
+        <v>15319.797736597591</v>
       </c>
       <c r="Q5">
-        <v>31905.654879752612</v>
+        <v>15316.398491176671</v>
       </c>
       <c r="R5">
-        <v>31797</v>
+        <v>15313.000000000005</v>
       </c>
       <c r="S5">
-        <v>31702.034439527859</v>
+        <v>15295.158473269763</v>
       </c>
       <c r="T5">
-        <v>31607.352505110874</v>
+        <v>15277.337734110613</v>
       </c>
       <c r="U5">
-        <v>31512.953349665757</v>
+        <v>15259.537758302477</v>
       </c>
       <c r="V5">
-        <v>31418.836128639137</v>
+        <v>15241.758521653497</v>
       </c>
       <c r="W5">
-        <v>31325</v>
+        <v>15224.000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -860,70 +869,70 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>436939</v>
+        <v>5351</v>
       </c>
       <c r="D6">
-        <v>436782.08734014427</v>
+        <v>5042.652940649542</v>
       </c>
       <c r="E6">
-        <v>436625.2310304491</v>
+        <v>4752.0741319083299</v>
       </c>
       <c r="F6">
-        <v>436468.43105067819</v>
+        <v>4478.2396926653255</v>
       </c>
       <c r="G6">
-        <v>436311.68738060247</v>
+        <v>4220.184742132742</v>
       </c>
       <c r="H6">
-        <v>436155.00000000006</v>
+        <v>3977</v>
       </c>
       <c r="I6">
-        <v>435974.04991871933</v>
+        <v>3778.0697544968248</v>
       </c>
       <c r="J6">
-        <v>435793.17490921798</v>
+        <v>3589.0900351631126</v>
       </c>
       <c r="K6">
-        <v>435612.37494035048</v>
+        <v>3409.5631149146848</v>
       </c>
       <c r="L6">
-        <v>435431.64998098434</v>
+        <v>3239.0161630644084</v>
       </c>
       <c r="M6">
-        <v>435250.99999999994</v>
+        <v>3076.9999999999991</v>
       </c>
       <c r="N6">
-        <v>435046.80850308534</v>
+        <v>2988.6724783304303</v>
       </c>
       <c r="O6">
-        <v>434842.71279955748</v>
+        <v>2902.8804623756114</v>
       </c>
       <c r="P6">
-        <v>434638.71284447645</v>
+        <v>2819.5511686009436</v>
       </c>
       <c r="Q6">
-        <v>434434.80859292328</v>
+        <v>2738.6139027760942</v>
       </c>
       <c r="R6">
-        <v>434231.00000000006</v>
+        <v>2660.0000000000005</v>
       </c>
       <c r="S6">
-        <v>434019.59425404365</v>
+        <v>2606.4900024228073</v>
       </c>
       <c r="T6">
-        <v>433808.29143116146</v>
+        <v>2554.0564408759569</v>
       </c>
       <c r="U6">
-        <v>433597.0914812453</v>
+        <v>2502.6776611905111</v>
       </c>
       <c r="V6">
-        <v>433385.99435421132</v>
+        <v>2452.3324448044964</v>
       </c>
       <c r="W6">
-        <v>433175.00000000012</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -931,70 +940,70 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>99848</v>
+        <v>9489</v>
       </c>
       <c r="D7">
-        <v>100099.33153706881</v>
+        <v>9285.4527947134738</v>
       </c>
       <c r="E7">
-        <v>100351.29571116115</v>
+        <v>9086.271851918249</v>
       </c>
       <c r="F7">
-        <v>100603.89411471387</v>
+        <v>8891.3635115313173</v>
       </c>
       <c r="G7">
-        <v>100857.12834417223</v>
+        <v>8700.6361225589499</v>
       </c>
       <c r="H7">
-        <v>101110.99999999996</v>
+        <v>8514</v>
       </c>
       <c r="I7">
-        <v>100906.17180754028</v>
+        <v>8350.4349866464017</v>
       </c>
       <c r="J7">
-        <v>100701.75855102646</v>
+        <v>8190.0122699328513</v>
       </c>
       <c r="K7">
-        <v>100497.75938989145</v>
+        <v>8032.6714822540052</v>
       </c>
       <c r="L7">
-        <v>100294.17348527095</v>
+        <v>7878.3534157447339</v>
       </c>
       <c r="M7">
-        <v>100091.00000000001</v>
+        <v>7727.0000000000018</v>
       </c>
       <c r="N7">
-        <v>99932.700069592829</v>
+        <v>7603.302475774547</v>
       </c>
       <c r="O7">
-        <v>99774.650500036951</v>
+        <v>7481.5851608799476</v>
       </c>
       <c r="P7">
-        <v>99616.850895371637</v>
+        <v>7361.8163551749212</v>
       </c>
       <c r="Q7">
-        <v>99459.300860262403</v>
+        <v>7243.9648659892628</v>
       </c>
       <c r="R7">
-        <v>99301.999999999985</v>
+        <v>7128</v>
       </c>
       <c r="S7">
-        <v>99149.532523685339</v>
+        <v>7023.3732749792407</v>
       </c>
       <c r="T7">
-        <v>98997.299144683246</v>
+        <v>6920.2822895191675</v>
       </c>
       <c r="U7">
-        <v>98845.299503562652</v>
+        <v>6818.7045016163129</v>
       </c>
       <c r="V7">
-        <v>98693.533241444311</v>
+        <v>6718.6177001448732</v>
       </c>
       <c r="W7">
-        <v>98542.000000000029</v>
+        <v>6619.9999999999991</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -1002,70 +1011,70 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>109515</v>
+        <v>11866</v>
       </c>
       <c r="D8">
-        <v>107112.69327735881</v>
+        <v>11744.121914991618</v>
       </c>
       <c r="E8">
-        <v>104763.08324092175</v>
+        <v>11623.495664435057</v>
       </c>
       <c r="F8">
-        <v>102465.01394306954</v>
+        <v>11504.108390485573</v>
       </c>
       <c r="G8">
-        <v>100217.3547928987</v>
+        <v>11385.947367363944</v>
       </c>
       <c r="H8">
-        <v>98019.000000000015</v>
+        <v>11269</v>
       </c>
       <c r="I8">
-        <v>97141.218718306365</v>
+        <v>11159.7002344054</v>
       </c>
       <c r="J8">
-        <v>96271.298157273952</v>
+        <v>11051.4605840614</v>
       </c>
       <c r="K8">
-        <v>95409.167922454144</v>
+        <v>10944.270766747009</v>
       </c>
       <c r="L8">
-        <v>94554.758249795836</v>
+        <v>10838.120599970074</v>
       </c>
       <c r="M8">
-        <v>93708</v>
+        <v>10733.000000000002</v>
       </c>
       <c r="N8">
-        <v>93040.971318267009</v>
+        <v>10637.516143085304</v>
       </c>
       <c r="O8">
-        <v>92378.690654443417</v>
+        <v>10542.881738041595</v>
       </c>
       <c r="P8">
-        <v>91721.124211370741</v>
+        <v>10449.08922790056</v>
       </c>
       <c r="Q8">
-        <v>91068.238432464146</v>
+        <v>10356.131122922852</v>
       </c>
       <c r="R8">
-        <v>90419.999999999971</v>
+        <v>10263.999999999998</v>
       </c>
       <c r="S8">
-        <v>89960.758678637852</v>
+        <v>10178.383536794627</v>
       </c>
       <c r="T8">
-        <v>89503.849834506924</v>
+        <v>10093.481237538181</v>
       </c>
       <c r="U8">
-        <v>89049.261621003301</v>
+        <v>10009.287145080287</v>
       </c>
       <c r="V8">
-        <v>88596.982251691734</v>
+        <v>9925.7953519617386</v>
       </c>
       <c r="W8">
-        <v>88147.000000000015</v>
+        <v>9842.9999999999982</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -1073,70 +1082,70 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>417121</v>
+        <v>8339</v>
       </c>
       <c r="D9">
-        <v>422038.28890604404</v>
+        <v>8378.4254391586601</v>
       </c>
       <c r="E9">
-        <v>427013.54595606908</v>
+        <v>8418.037275397648</v>
       </c>
       <c r="F9">
-        <v>432047.45451560046</v>
+        <v>8457.8363899721207</v>
       </c>
       <c r="G9">
-        <v>437140.70600611309</v>
+        <v>8497.8236683036648</v>
       </c>
       <c r="H9">
-        <v>442294</v>
+        <v>8537.9999999999982</v>
       </c>
       <c r="I9">
-        <v>442677.13564490434</v>
+        <v>8571.3386244249468</v>
       </c>
       <c r="J9">
-        <v>443060.6031797335</v>
+        <v>8604.8074273318034</v>
       </c>
       <c r="K9">
-        <v>443444.40289198596</v>
+        <v>8638.4069170330004</v>
       </c>
       <c r="L9">
-        <v>443828.53506940923</v>
+        <v>8672.1376038257895</v>
       </c>
       <c r="M9">
-        <v>444213.00000000012</v>
+        <v>8706</v>
       </c>
       <c r="N9">
-        <v>443388.34382428735</v>
+        <v>8749.9539336668477</v>
       </c>
       <c r="O9">
-        <v>442565.21857587341</v>
+        <v>8794.1297773135702</v>
       </c>
       <c r="P9">
-        <v>441743.62141267874</v>
+        <v>8838.5286512958464</v>
       </c>
       <c r="Q9">
-        <v>440923.54949789995</v>
+        <v>8883.1516816256881</v>
       </c>
       <c r="R9">
-        <v>440105.00000000012</v>
+        <v>8927.9999999999964</v>
       </c>
       <c r="S9">
-        <v>438010.76380207005</v>
+        <v>8986.2353168922909</v>
       </c>
       <c r="T9">
-        <v>435926.49301069696</v>
+        <v>9044.8504895343067</v>
       </c>
       <c r="U9">
-        <v>433852.14020557166</v>
+        <v>9103.8479956388564</v>
       </c>
       <c r="V9">
-        <v>431787.65819203423</v>
+        <v>9163.2303290803065</v>
       </c>
       <c r="W9">
-        <v>429733.00000000012</v>
+        <v>9223.0000000000018</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -1144,70 +1153,70 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>204935</v>
+        <v>2444</v>
       </c>
       <c r="D10">
-        <v>200658.17930130687</v>
+        <v>2393.1256266899063</v>
       </c>
       <c r="E10">
-        <v>196470.6122454213</v>
+        <v>2343.3102557773964</v>
       </c>
       <c r="F10">
-        <v>192370.43618405488</v>
+        <v>2294.5318430385296</v>
       </c>
       <c r="G10">
-        <v>188355.82734081877</v>
+        <v>2246.7688031225562</v>
       </c>
       <c r="H10">
-        <v>184425.00000000006</v>
+        <v>2199.9999999999991</v>
       </c>
       <c r="I10">
-        <v>184466.38142543961</v>
+        <v>2214.0201621698616</v>
       </c>
       <c r="J10">
-        <v>184507.77213607577</v>
+        <v>2228.1296720430273</v>
       </c>
       <c r="K10">
-        <v>184549.17213399187</v>
+        <v>2242.3290990146288</v>
       </c>
       <c r="L10">
-        <v>184590.58142127184</v>
+        <v>2256.6190161084401</v>
       </c>
       <c r="M10">
-        <v>184632</v>
+        <v>2271.0000000000009</v>
       </c>
       <c r="N10">
-        <v>185059.0201865196</v>
+        <v>2297.952606074191</v>
       </c>
       <c r="O10">
-        <v>185487.02799295174</v>
+        <v>2325.2250901643179</v>
       </c>
       <c r="P10">
-        <v>185916.02570348143</v>
+        <v>2352.8212486359271</v>
       </c>
       <c r="Q10">
-        <v>186346.0156075765</v>
+        <v>2380.7449229104627</v>
       </c>
       <c r="R10">
-        <v>186776.99999999997</v>
+        <v>2408.9999999999986</v>
       </c>
       <c r="S10">
-        <v>186923.76915659828</v>
+        <v>2440.7518819596071</v>
       </c>
       <c r="T10">
-        <v>187070.65364423482</v>
+        <v>2472.9222703567302</v>
       </c>
       <c r="U10">
-        <v>187217.65355353657</v>
+        <v>2505.5166813254518</v>
       </c>
       <c r="V10">
-        <v>187364.76897520179</v>
+        <v>2538.5407037053906</v>
       </c>
       <c r="W10">
-        <v>187511.99999999994</v>
+        <v>2571.9999999999986</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -1215,70 +1224,70 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>532082</v>
+        <v>8545</v>
       </c>
       <c r="D11">
-        <v>541483.07330048934</v>
+        <v>8722.8417089173836</v>
       </c>
       <c r="E11">
-        <v>551050.24915509846</v>
+        <v>8904.3847254334396</v>
       </c>
       <c r="F11">
-        <v>560786.46234133665</v>
+        <v>9089.7060825345434</v>
       </c>
       <c r="G11">
-        <v>570694.69948973297</v>
+        <v>9278.8844164461498</v>
       </c>
       <c r="H11">
-        <v>580777.99999999965</v>
+        <v>9472.0000000000018</v>
       </c>
       <c r="I11">
-        <v>585177.63499021984</v>
+        <v>9630.2248310804771</v>
       </c>
       <c r="J11">
-        <v>589610.59904601576</v>
+        <v>9791.0927256291179</v>
       </c>
       <c r="K11">
-        <v>594077.14464892657</v>
+        <v>9954.6478346457934</v>
       </c>
       <c r="L11">
-        <v>598577.52619314368</v>
+        <v>10120.935046649854</v>
       </c>
       <c r="M11">
-        <v>603112.00000000035</v>
+        <v>10290.000000000007</v>
       </c>
       <c r="N11">
-        <v>606356.89492446627</v>
+        <v>10422.731326525831</v>
       </c>
       <c r="O11">
-        <v>609619.2482033855</v>
+        <v>10557.174762385122</v>
       </c>
       <c r="P11">
-        <v>612899.1537671152</v>
+        <v>10693.352392178747</v>
       </c>
       <c r="Q11">
-        <v>616196.70605138177</v>
+        <v>10831.28658537817</v>
       </c>
       <c r="R11">
-        <v>619511.99999999988</v>
+        <v>10971.000000000004</v>
       </c>
       <c r="S11">
-        <v>621816.98401161213</v>
+        <v>11074.045997314995</v>
       </c>
       <c r="T11">
-        <v>624130.54404966731</v>
+        <v>11178.059862423504</v>
       </c>
       <c r="U11">
-        <v>626452.71202251245</v>
+        <v>11283.050686101396</v>
       </c>
       <c r="V11">
-        <v>628783.51995721413</v>
+        <v>11389.027644510381</v>
       </c>
       <c r="W11">
-        <v>631123.00000000023</v>
+        <v>11496.000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -1286,70 +1295,70 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>341390</v>
+        <v>76675</v>
       </c>
       <c r="D12">
-        <v>333865.1052428371</v>
+        <v>78723.570380748075</v>
       </c>
       <c r="E12">
-        <v>326506.07369521866</v>
+        <v>80826.873602772685</v>
       </c>
       <c r="F12">
-        <v>319309.24941175693</v>
+        <v>82986.371995092326</v>
       </c>
       <c r="G12">
-        <v>312271.05703115952</v>
+        <v>85203.566956616778</v>
       </c>
       <c r="H12">
-        <v>305388.00000000017</v>
+        <v>87480.000000000029</v>
       </c>
       <c r="I12">
-        <v>301382.70667751809</v>
+        <v>88561.906105629489</v>
       </c>
       <c r="J12">
-        <v>297429.94447806367</v>
+        <v>89657.19265046106</v>
       </c>
       <c r="K12">
-        <v>293529.02443364757</v>
+        <v>90766.025116649136</v>
       </c>
       <c r="L12">
-        <v>289679.26661238837</v>
+        <v>91888.571032943408</v>
       </c>
       <c r="M12">
-        <v>285880.00000000006</v>
+        <v>93025</v>
       </c>
       <c r="N12">
-        <v>285102.38110700197</v>
+        <v>93575.837800767986</v>
       </c>
       <c r="O12">
-        <v>284326.87740619207</v>
+        <v>94129.937329918175</v>
       </c>
       <c r="P12">
-        <v>283553.48314406042</v>
+        <v>94687.317901433795</v>
       </c>
       <c r="Q12">
-        <v>282782.1925827472</v>
+        <v>95247.998943663784</v>
       </c>
       <c r="R12">
-        <v>282013.00000000006</v>
+        <v>95812.000000000029</v>
       </c>
       <c r="S12">
-        <v>281539.81476173591</v>
+        <v>95802.398075654157</v>
       </c>
       <c r="T12">
-        <v>281067.42347364331</v>
+        <v>95792.797113577661</v>
       </c>
       <c r="U12">
-        <v>280595.82480356551</v>
+        <v>95783.197113674076</v>
       </c>
       <c r="V12">
-        <v>280125.01742158108</v>
+        <v>95773.598075846996</v>
       </c>
       <c r="W12">
-        <v>279654.99999999994</v>
+        <v>95763.999999999985</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -1357,70 +1366,70 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>1483502</v>
+        <v>14084</v>
       </c>
       <c r="D13">
-        <v>1481535.3928346254</v>
+        <v>14143.691869805336</v>
       </c>
       <c r="E13">
-        <v>1479571.3927056706</v>
+        <v>14203.636730190114</v>
       </c>
       <c r="F13">
-        <v>1477609.996157113</v>
+        <v>14263.835653398064</v>
       </c>
       <c r="G13">
-        <v>1475651.1997375113</v>
+        <v>14324.289716217387</v>
       </c>
       <c r="H13">
-        <v>1473695</v>
+        <v>14385.000000000002</v>
       </c>
       <c r="I13">
-        <v>1467533.8992941196</v>
+        <v>14459.034019128192</v>
       </c>
       <c r="J13">
-        <v>1461398.5564023785</v>
+        <v>14533.449062655987</v>
       </c>
       <c r="K13">
-        <v>1455288.8636386632</v>
+        <v>14608.247091568277</v>
       </c>
       <c r="L13">
-        <v>1449204.7137670657</v>
+        <v>14683.430076942384</v>
       </c>
       <c r="M13">
-        <v>1443146.0000000002</v>
+        <v>14759.000000000002</v>
       </c>
       <c r="N13">
-        <v>1435784.2754252281</v>
+        <v>14827.756390557191</v>
       </c>
       <c r="O13">
-        <v>1428460.1042156145</v>
+        <v>14896.833090162589</v>
       </c>
       <c r="P13">
-        <v>1421173.2948052809</v>
+        <v>14966.231591010379</v>
       </c>
       <c r="Q13">
-        <v>1413923.6566055578</v>
+        <v>15035.953392246296</v>
       </c>
       <c r="R13">
-        <v>1406710.9999999998</v>
+        <v>15106.000000000007</v>
       </c>
       <c r="S13">
-        <v>1399926.879495238</v>
+        <v>15194.164843268145</v>
       </c>
       <c r="T13">
-        <v>1393175.4766496278</v>
+        <v>15282.844252906507</v>
       </c>
       <c r="U13">
-        <v>1386456.6336762875</v>
+        <v>15372.041232136547</v>
       </c>
       <c r="V13">
-        <v>1379770.1935492915</v>
+        <v>15461.758801707763</v>
       </c>
       <c r="W13">
-        <v>1373116</v>
+        <v>15551.999999999995</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -1428,70 +1437,70 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>1014499</v>
+        <v>29949</v>
       </c>
       <c r="D14">
-        <v>1019510.2474529553</v>
+        <v>30573.414316540915</v>
       </c>
       <c r="E14">
-        <v>1024546.2486030899</v>
+        <v>31210.847205945742</v>
       </c>
       <c r="F14">
-        <v>1029607.1257244544</v>
+        <v>31861.570095750529</v>
       </c>
       <c r="G14">
-        <v>1034693.0016950875</v>
+        <v>32525.860072553045</v>
       </c>
       <c r="H14">
-        <v>1039803.9999999998</v>
+        <v>33203.999999999993</v>
       </c>
       <c r="I14">
-        <v>1044046.439834794</v>
+        <v>33766.795526869639</v>
       </c>
       <c r="J14">
-        <v>1048306.1889853359</v>
+        <v>34339.130229894698</v>
       </c>
       <c r="K14">
-        <v>1052583.3180742916</v>
+        <v>34921.16579458506</v>
       </c>
       <c r="L14">
-        <v>1056877.8980124702</v>
+        <v>35513.066646960244</v>
       </c>
       <c r="M14">
-        <v>1061190</v>
+        <v>36115.000000000015</v>
       </c>
       <c r="N14">
-        <v>1064584.2176212636</v>
+        <v>36364.917110605915</v>
       </c>
       <c r="O14">
-        <v>1067989.2916520867</v>
+        <v>36616.56365668666</v>
       </c>
       <c r="P14">
-        <v>1071405.2568167096</v>
+        <v>36869.951605998489</v>
       </c>
       <c r="Q14">
-        <v>1074832.1479504385</v>
+        <v>37125.093009114949</v>
       </c>
       <c r="R14">
-        <v>1078269.9999999998</v>
+        <v>37382.000000000007</v>
       </c>
       <c r="S14">
-        <v>1080904.0988758621</v>
+        <v>37381.399980738468</v>
       </c>
       <c r="T14">
-        <v>1083544.6325749946</v>
+        <v>37380.799971107852</v>
       </c>
       <c r="U14">
-        <v>1086191.6168169861</v>
+        <v>37380.199971108006</v>
       </c>
       <c r="V14">
-        <v>1088845.0673598265</v>
+        <v>37379.599980738771</v>
       </c>
       <c r="W14">
-        <v>1091505.0000000007</v>
+        <v>37378.999999999993</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -1499,70 +1508,70 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>662075</v>
+        <v>3626</v>
       </c>
       <c r="D15">
-        <v>657783.93655929482</v>
+        <v>3723.6022658806069</v>
       </c>
       <c r="E15">
-        <v>653520.68450771039</v>
+        <v>3823.8317248955295</v>
       </c>
       <c r="F15">
-        <v>649285.06359310762</v>
+        <v>3926.7590940891187</v>
       </c>
       <c r="G15">
-        <v>645076.89473160356</v>
+        <v>4032.4569940202764</v>
       </c>
       <c r="H15">
-        <v>640896</v>
+        <v>4141.0000000000009</v>
       </c>
       <c r="I15">
-        <v>637995.46434764436</v>
+        <v>4226.5881631182692</v>
       </c>
       <c r="J15">
-        <v>635108.05579714396</v>
+        <v>4313.945303214553</v>
       </c>
       <c r="K15">
-        <v>632233.71493850567</v>
+        <v>4403.1079823487762</v>
       </c>
       <c r="L15">
-        <v>629372.38263061119</v>
+        <v>4494.1135182629559</v>
       </c>
       <c r="M15">
-        <v>626524.00000000023</v>
+        <v>4587.0000000000018</v>
       </c>
       <c r="N15">
-        <v>624286.06932221993</v>
+        <v>4646.6293925997843</v>
       </c>
       <c r="O15">
-        <v>622056.13248620578</v>
+        <v>4707.033946407726</v>
       </c>
       <c r="P15">
-        <v>619834.16093812126</v>
+        <v>4768.2237382478961</v>
       </c>
       <c r="Q15">
-        <v>617620.12622612377</v>
+        <v>4830.2089759395458</v>
       </c>
       <c r="R15">
-        <v>615414.00000000023</v>
+        <v>4893</v>
       </c>
       <c r="S15">
-        <v>613362.97434424469</v>
+        <v>4961.0790156904859</v>
       </c>
       <c r="T15">
-        <v>611318.78425973176</v>
+        <v>5030.1052523859562</v>
       </c>
       <c r="U15">
-        <v>609281.40696515958</v>
+        <v>5100.0918892962318</v>
       </c>
       <c r="V15">
-        <v>607250.81975515094</v>
+        <v>5171.0522890007724</v>
       </c>
       <c r="W15">
-        <v>605227.00000000023</v>
+        <v>5242.9999999999973</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -1570,70 +1579,70 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C16">
-        <v>91437</v>
+        <v>19402</v>
       </c>
       <c r="D16">
-        <v>90260.090851386121</v>
+        <v>19447.189010583446</v>
       </c>
       <c r="E16">
-        <v>89098.330003176801</v>
+        <v>19492.483270454468</v>
       </c>
       <c r="F16">
-        <v>87951.52247770071</v>
+        <v>19537.88302474816</v>
       </c>
       <c r="G16">
-        <v>86819.475806894305</v>
+        <v>19583.388519170567</v>
       </c>
       <c r="H16">
-        <v>85702</v>
+        <v>19628.999999999996</v>
       </c>
       <c r="I16">
-        <v>85155.679040756222</v>
+        <v>19856.657639495224</v>
       </c>
       <c r="J16">
-        <v>84612.840690909055</v>
+        <v>20086.955658063278</v>
       </c>
       <c r="K16">
-        <v>84073.462750013874</v>
+        <v>20319.924678887564</v>
       </c>
       <c r="L16">
-        <v>83537.523159146294</v>
+        <v>20555.595680319951</v>
       </c>
       <c r="M16">
-        <v>83005.000000000015</v>
+        <v>20794.000000000011</v>
       </c>
       <c r="N16">
-        <v>82795.141524626219</v>
+        <v>21005.839558733544</v>
       </c>
       <c r="O16">
-        <v>82585.813626683754</v>
+        <v>21219.837239937242</v>
       </c>
       <c r="P16">
-        <v>82377.014964733273</v>
+        <v>21436.015029554725</v>
       </c>
       <c r="Q16">
-        <v>82168.744200726971</v>
+        <v>21654.39513751214</v>
       </c>
       <c r="R16">
-        <v>81960.999999999985</v>
+        <v>21874.999999999989</v>
       </c>
       <c r="S16">
-        <v>81867.386398343268</v>
+        <v>22056.560993473951</v>
       </c>
       <c r="T16">
-        <v>81773.879719569552</v>
+        <v>22239.628930689676</v>
       </c>
       <c r="U16">
-        <v>81680.479841554479</v>
+        <v>22424.216319176445</v>
       </c>
       <c r="V16">
-        <v>81587.186642313158</v>
+        <v>22610.335770275164</v>
       </c>
       <c r="W16">
-        <v>81494.000000000015</v>
+        <v>22798</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -1641,70 +1650,70 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>57076</v>
+        <v>6126</v>
       </c>
       <c r="D17">
-        <v>56951.457671056756</v>
+        <v>6423.8036082910312</v>
       </c>
       <c r="E17">
-        <v>56827.187098923707</v>
+        <v>6736.0843613928946</v>
       </c>
       <c r="F17">
-        <v>56703.187690615603</v>
+        <v>7063.5460376213623</v>
       </c>
       <c r="G17">
-        <v>56579.458854441109</v>
+        <v>7406.9266281100108</v>
       </c>
       <c r="H17">
-        <v>56456</v>
+        <v>7767.0000000000018</v>
       </c>
       <c r="I17">
-        <v>56624.194831108376</v>
+        <v>7995.0137115979269</v>
       </c>
       <c r="J17">
-        <v>56792.890751582127</v>
+        <v>8229.7211598608028</v>
       </c>
       <c r="K17">
-        <v>56962.089254276594</v>
+        <v>8471.3188509997053</v>
       </c>
       <c r="L17">
-        <v>57131.79183649466</v>
+        <v>8720.0090600052317</v>
       </c>
       <c r="M17">
-        <v>57302.000000000015</v>
+        <v>8975.9999999999964</v>
       </c>
       <c r="N17">
-        <v>57490.357620783732</v>
+        <v>9112.7681122571012</v>
       </c>
       <c r="O17">
-        <v>57679.334392614677</v>
+        <v>9251.6201724342536</v>
       </c>
       <c r="P17">
-        <v>57868.932350706578</v>
+        <v>9392.5879338317081</v>
       </c>
       <c r="Q17">
-        <v>58059.153536963146</v>
+        <v>9535.7036335775847</v>
       </c>
       <c r="R17">
-        <v>58250.000000000036</v>
+        <v>9680.9999999999982</v>
       </c>
       <c r="S17">
-        <v>58481.748617240191</v>
+        <v>9769.9503367385514</v>
       </c>
       <c r="T17">
-        <v>58714.419250301718</v>
+        <v>9859.7179611959236</v>
       </c>
       <c r="U17">
-        <v>58948.015567440234</v>
+        <v>9950.3103827221639</v>
       </c>
       <c r="V17">
-        <v>59182.541251505601</v>
+        <v>10041.735179664242</v>
       </c>
       <c r="W17">
-        <v>59417.999999999971</v>
+        <v>10134.000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -1712,70 +1721,70 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C18">
-        <v>393253</v>
+        <v>17116</v>
       </c>
       <c r="D18">
-        <v>390851.65148837148</v>
+        <v>17447.507411195937</v>
       </c>
       <c r="E18">
-        <v>388464.96650041424</v>
+        <v>17785.435549412079</v>
       </c>
       <c r="F18">
-        <v>386092.85549522017</v>
+        <v>18129.908773061165</v>
       </c>
       <c r="G18">
-        <v>383735.22947865108</v>
+        <v>18481.053849163993</v>
       </c>
       <c r="H18">
-        <v>381391.99999999994</v>
+        <v>18838.999999999996</v>
       </c>
       <c r="I18">
-        <v>379853.23335949611</v>
+        <v>19132.134607000386</v>
       </c>
       <c r="J18">
-        <v>378320.67503687495</v>
+        <v>19429.830384860226</v>
       </c>
       <c r="K18">
-        <v>376794.29998401686</v>
+        <v>19732.158305341683</v>
       </c>
       <c r="L18">
-        <v>375274.08325386146</v>
+        <v>20039.190444526659</v>
       </c>
       <c r="M18">
-        <v>373760.00000000006</v>
+        <v>20350.999999999996</v>
       </c>
       <c r="N18">
-        <v>372521.82357371872</v>
+        <v>20629.473975371839</v>
       </c>
       <c r="O18">
-        <v>371287.74892628647</v>
+        <v>20911.758463984275</v>
       </c>
       <c r="P18">
-        <v>370057.76246950252</v>
+        <v>21197.905607195</v>
       </c>
       <c r="Q18">
-        <v>368831.85066018067</v>
+        <v>21487.968259840698</v>
       </c>
       <c r="R18">
-        <v>367610</v>
+        <v>21781.999999999989</v>
       </c>
       <c r="S18">
-        <v>366727.77566368505</v>
+        <v>22050.688971963147</v>
       </c>
       <c r="T18">
-        <v>365847.66857058869</v>
+        <v>22322.692321102615</v>
       </c>
       <c r="U18">
-        <v>364969.67363955564</v>
+        <v>22598.050931478461</v>
       </c>
       <c r="V18">
-        <v>364093.78580162482</v>
+        <v>22876.806191470645</v>
       </c>
       <c r="W18">
-        <v>363220.00000000017</v>
+        <v>23159</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -1783,70 +1792,70 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>265014</v>
+        <v>1346</v>
       </c>
       <c r="D19">
-        <v>272748.20033796364</v>
+        <v>1339.5382553106715</v>
       </c>
       <c r="E19">
-        <v>280708.11650553538</v>
+        <v>1333.1075315310236</v>
       </c>
       <c r="F19">
-        <v>288900.33582053852</v>
+        <v>1326.7076797389177</v>
       </c>
       <c r="G19">
-        <v>297331.63784586929</v>
+        <v>1320.3385517271463</v>
       </c>
       <c r="H19">
-        <v>306009</v>
+        <v>1314.0000000000002</v>
       </c>
       <c r="I19">
-        <v>309496.01903050183</v>
+        <v>1307.9444426615075</v>
       </c>
       <c r="J19">
-        <v>313022.77317245165</v>
+        <v>1301.9167923052676</v>
       </c>
       <c r="K19">
-        <v>316589.71521347918</v>
+        <v>1295.9169203222002</v>
       </c>
       <c r="L19">
-        <v>320197.30310079805</v>
+        <v>1289.944698695919</v>
       </c>
       <c r="M19">
-        <v>323845.99999999988</v>
+        <v>1284</v>
       </c>
       <c r="N19">
-        <v>325970.5410871405</v>
+        <v>1279.1637043269216</v>
       </c>
       <c r="O19">
-        <v>328109.01989415695</v>
+        <v>1274.3456249745886</v>
       </c>
       <c r="P19">
-        <v>330261.52785728307</v>
+        <v>1269.5456933296734</v>
       </c>
       <c r="Q19">
-        <v>332428.15701260563</v>
+        <v>1264.7638410372858</v>
       </c>
       <c r="R19">
-        <v>334608.99999999988</v>
+        <v>1260.0000000000002</v>
       </c>
       <c r="S19">
-        <v>336263.36008077493</v>
+        <v>1257.1874719418272</v>
       </c>
       <c r="T19">
-        <v>337925.89958074322</v>
+        <v>1254.3812219107006</v>
       </c>
       <c r="U19">
-        <v>339596.65894025343</v>
+        <v>1251.5812358930268</v>
       </c>
       <c r="V19">
-        <v>341275.6787995976</v>
+        <v>1248.7874999064938</v>
       </c>
       <c r="W19">
-        <v>342962.99999999994</v>
+        <v>1245.9999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -1854,70 +1863,70 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>279198</v>
+        <v>42496</v>
       </c>
       <c r="D20">
-        <v>281561.83284343575</v>
+        <v>43142.0554650337</v>
       </c>
       <c r="E20">
-        <v>283945.67910284048</v>
+        <v>43797.932740682518</v>
       </c>
       <c r="F20">
-        <v>286349.70822201384</v>
+        <v>44463.781145339344</v>
       </c>
       <c r="G20">
-        <v>288774.09107935324</v>
+        <v>45139.752267445168</v>
       </c>
       <c r="H20">
-        <v>291218.99999999983</v>
+        <v>45826.000000000007</v>
       </c>
       <c r="I20">
-        <v>293432.4946515492</v>
+        <v>46243.907988985615</v>
       </c>
       <c r="J20">
-        <v>295662.81361254398</v>
+        <v>46665.627069649709</v>
       </c>
       <c r="K20">
-        <v>297910.08476103825</v>
+        <v>47091.191997058384</v>
       </c>
       <c r="L20">
-        <v>300174.43694706023</v>
+        <v>47520.637843224889</v>
       </c>
       <c r="M20">
-        <v>302456.00000000017</v>
+        <v>47953.999999999993</v>
       </c>
       <c r="N20">
-        <v>304135.24964309583</v>
+        <v>48282.858476875081</v>
       </c>
       <c r="O20">
-        <v>305823.82255755621</v>
+        <v>48613.972196228628</v>
       </c>
       <c r="P20">
-        <v>307521.77050661319</v>
+        <v>48947.35662404068</v>
       </c>
       <c r="Q20">
-        <v>309229.14554089069</v>
+        <v>49283.027332353711</v>
       </c>
       <c r="R20">
-        <v>310946</v>
+        <v>49621.000000000007</v>
       </c>
       <c r="S20">
-        <v>312188.82527317555</v>
+        <v>50032.517552737394</v>
       </c>
       <c r="T20">
-        <v>313436.61801549251</v>
+        <v>50447.447908445523</v>
       </c>
       <c r="U20">
-        <v>314689.39808151143</v>
+        <v>50865.819370228448</v>
       </c>
       <c r="V20">
-        <v>315947.18540514994</v>
+        <v>51287.660475913915</v>
       </c>
       <c r="W20">
-        <v>317209.99999999988</v>
+        <v>51712.999999999978</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -1925,70 +1934,70 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>380150</v>
+        <v>13959</v>
       </c>
       <c r="D21">
-        <v>371841.03311540553</v>
+        <v>14272.407236899631</v>
       </c>
       <c r="E21">
-        <v>363713.67593931896</v>
+        <v>14592.851087893472</v>
       </c>
       <c r="F21">
-        <v>355763.95901480515</v>
+        <v>14920.489538924669</v>
       </c>
       <c r="G21">
-        <v>347987.99964564497</v>
+        <v>15255.484123034148</v>
       </c>
       <c r="H21">
-        <v>340382</v>
+        <v>15598</v>
       </c>
       <c r="I21">
-        <v>338780.39870514901</v>
+        <v>15625.502841239932</v>
       </c>
       <c r="J21">
-        <v>337186.33343367081</v>
+        <v>15653.054176278829</v>
       </c>
       <c r="K21">
-        <v>335599.76872627321</v>
+        <v>15680.654090622351</v>
       </c>
       <c r="L21">
-        <v>334020.66929051076</v>
+        <v>15708.302669926919</v>
       </c>
       <c r="M21">
-        <v>332448.99999999988</v>
+        <v>15735.999999999993</v>
       </c>
       <c r="N21">
-        <v>330720.51965640654</v>
+        <v>15694.582550061106</v>
       </c>
       <c r="O21">
-        <v>329001.02608762123</v>
+        <v>15653.274111634633</v>
       </c>
       <c r="P21">
-        <v>327290.47256929352</v>
+        <v>15612.074397800216</v>
       </c>
       <c r="Q21">
-        <v>325588.81262000371</v>
+        <v>15570.983122392669</v>
       </c>
       <c r="R21">
-        <v>323896</v>
+        <v>15529.999999999998</v>
       </c>
       <c r="S21">
-        <v>322441.39335931686</v>
+        <v>15533.59833213206</v>
       </c>
       <c r="T21">
-        <v>320993.31931082107</v>
+        <v>15537.197498004889</v>
       </c>
       <c r="U21">
-        <v>319551.74851684878</v>
+        <v>15540.797497811665</v>
       </c>
       <c r="V21">
-        <v>318116.65177149064</v>
+        <v>15544.398331745613</v>
       </c>
       <c r="W21">
-        <v>316688.00000000012</v>
+        <v>15548.000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -1996,70 +2005,70 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>368538</v>
+        <v>17698</v>
       </c>
       <c r="D22">
-        <v>363638.86751751619</v>
+        <v>17584.144473479555</v>
       </c>
       <c r="E22">
-        <v>358804.86128817569</v>
+        <v>17471.021407176038</v>
       </c>
       <c r="F22">
-        <v>354035.11556097795</v>
+        <v>17358.626088995225</v>
       </c>
       <c r="G22">
-        <v>349328.77609371895</v>
+        <v>17246.953837156932</v>
       </c>
       <c r="H22">
-        <v>344684.99999999988</v>
+        <v>17136.000000000004</v>
       </c>
       <c r="I22">
-        <v>341298.0905970668</v>
+        <v>17209.565641104378</v>
       </c>
       <c r="J22">
-        <v>337944.46130584041</v>
+        <v>17283.44710291085</v>
       </c>
       <c r="K22">
-        <v>334623.78511260322</v>
+        <v>17357.645741252309</v>
       </c>
       <c r="L22">
-        <v>331335.73821690719</v>
+        <v>17432.162917782298</v>
       </c>
       <c r="M22">
-        <v>328080</v>
+        <v>17507.000000000004</v>
       </c>
       <c r="N22">
-        <v>327214.24281767948</v>
+        <v>17637.053351366005</v>
       </c>
       <c r="O22">
-        <v>326350.77024734003</v>
+        <v>17768.072823380979</v>
       </c>
       <c r="P22">
-        <v>325489.57626021048</v>
+        <v>17900.065593015748</v>
       </c>
       <c r="Q22">
-        <v>324630.65484342881</v>
+        <v>18033.03889055633</v>
       </c>
       <c r="R22">
-        <v>323774.00000000006</v>
+        <v>18167</v>
       </c>
       <c r="S22">
-        <v>324435.2931567452</v>
+        <v>18237.845294587249</v>
       </c>
       <c r="T22">
-        <v>325097.93697363965</v>
+        <v>18308.966862404264</v>
       </c>
       <c r="U22">
-        <v>325761.9342093431</v>
+        <v>18380.365780825316</v>
       </c>
       <c r="V22">
-        <v>326427.28762814985</v>
+        <v>18452.043131426075</v>
       </c>
       <c r="W22">
-        <v>327093.99999999994</v>
+        <v>18524</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2067,70 +2076,70 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>139266</v>
+        <v>4115</v>
       </c>
       <c r="D23">
-        <v>141615.38435291013</v>
+        <v>4271.6160233797746</v>
       </c>
       <c r="E23">
-        <v>144004.4022620199</v>
+        <v>4434.1928192454043</v>
       </c>
       <c r="F23">
-        <v>146433.72233601188</v>
+        <v>4602.9572533278742</v>
       </c>
       <c r="G23">
-        <v>148904.02446283834</v>
+        <v>4778.1448258195633</v>
       </c>
       <c r="H23">
-        <v>151415.99999999988</v>
+        <v>4960.0000000000018</v>
       </c>
       <c r="I23">
-        <v>152854.7953016363</v>
+        <v>5127.8488423883982</v>
       </c>
       <c r="J23">
-        <v>154307.26242078203</v>
+        <v>5301.3777722548457</v>
       </c>
       <c r="K23">
-        <v>155773.53127070132</v>
+        <v>5480.7790065565714</v>
       </c>
       <c r="L23">
-        <v>157253.73299912884</v>
+        <v>5666.2512669672878</v>
       </c>
       <c r="M23">
-        <v>158748.00000000006</v>
+        <v>5858</v>
       </c>
       <c r="N23">
-        <v>158956.45184485978</v>
+        <v>6031.0672805559789</v>
       </c>
       <c r="O23">
-        <v>159165.17740763491</v>
+        <v>6209.2476173767309</v>
       </c>
       <c r="P23">
-        <v>159374.17704774413</v>
+        <v>6392.6920693122174</v>
       </c>
       <c r="Q23">
-        <v>159583.45112507811</v>
+        <v>6581.5561580571193</v>
       </c>
       <c r="R23">
-        <v>159793.00000000009</v>
+        <v>6776.0000000000009</v>
       </c>
       <c r="S23">
-        <v>160275.67521408695</v>
+        <v>6952.5563710610741</v>
       </c>
       <c r="T23">
-        <v>160759.80841045282</v>
+        <v>7133.7131187694704</v>
       </c>
       <c r="U23">
-        <v>161245.40399311975</v>
+        <v>7319.5901111603662</v>
       </c>
       <c r="V23">
-        <v>161732.46637941274</v>
+        <v>7510.3103395666521</v>
       </c>
       <c r="W23">
-        <v>162220.99999999997</v>
+        <v>7705.9999999999973</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -2138,70 +2147,70 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C24">
-        <v>34910</v>
+        <v>40321</v>
       </c>
       <c r="D24">
-        <v>35647.200372119521</v>
+        <v>40672.613885919782</v>
       </c>
       <c r="E24">
-        <v>36399.968329133146</v>
+        <v>41027.293973689011</v>
       </c>
       <c r="F24">
-        <v>37168.632614363043</v>
+        <v>41385.06700171069</v>
       </c>
       <c r="G24">
-        <v>37953.528913259695</v>
+        <v>41745.959941556473</v>
       </c>
       <c r="H24">
-        <v>38755</v>
+        <v>42110.000000000015</v>
       </c>
       <c r="I24">
-        <v>39477.178921442246</v>
+        <v>42355.715672230348</v>
       </c>
       <c r="J24">
-        <v>40212.815265012614</v>
+        <v>42602.865117711219</v>
       </c>
       <c r="K24">
-        <v>40962.159802652735</v>
+        <v>42851.456702639669</v>
       </c>
       <c r="L24">
-        <v>41725.467979306704</v>
+        <v>43101.498842030283</v>
       </c>
       <c r="M24">
-        <v>42503</v>
+        <v>43353.000000000007</v>
       </c>
       <c r="N24">
-        <v>43221.120165209744</v>
+        <v>43413.033505595638</v>
       </c>
       <c r="O24">
-        <v>43951.373510940408</v>
+        <v>43473.150143195846</v>
       </c>
       <c r="P24">
-        <v>44693.965036406174</v>
+        <v>43533.35002791851</v>
       </c>
       <c r="Q24">
-        <v>45449.103204437197</v>
+        <v>43593.63327504092</v>
       </c>
       <c r="R24">
-        <v>46216.999999999978</v>
+        <v>43654.000000000007</v>
       </c>
       <c r="S24">
-        <v>46933.628992512888</v>
+        <v>43807.31925151094</v>
       </c>
       <c r="T24">
-        <v>47661.369851068797</v>
+        <v>43961.176982723257</v>
       </c>
       <c r="U24">
-        <v>48400.394873423247</v>
+        <v>44115.575084856646</v>
       </c>
       <c r="V24">
-        <v>49150.879028936746</v>
+        <v>44270.515455773057</v>
       </c>
       <c r="W24">
-        <v>49912.999999999993</v>
+        <v>44425.999999999993</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -2209,70 +2218,70 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>110096</v>
+        <v>1142</v>
       </c>
       <c r="D25">
-        <v>109894.46350319541</v>
+        <v>1196.5364559879768</v>
       </c>
       <c r="E25">
-        <v>109693.29592950833</v>
+        <v>1253.6773121788681</v>
       </c>
       <c r="F25">
-        <v>109492.49660360564</v>
+        <v>1313.5469422653546</v>
       </c>
       <c r="G25">
-        <v>109292.0648513905</v>
+        <v>1376.2756594326013</v>
       </c>
       <c r="H25">
-        <v>109092</v>
+        <v>1442.0000000000002</v>
       </c>
       <c r="I25">
-        <v>108447.83753243003</v>
+        <v>1503.8599650177623</v>
       </c>
       <c r="J25">
-        <v>107807.47869193286</v>
+        <v>1568.3736438163837</v>
       </c>
       <c r="K25">
-        <v>107170.90101898991</v>
+        <v>1635.6548773401437</v>
       </c>
       <c r="L25">
-        <v>106538.08218670075</v>
+        <v>1705.8223901649658</v>
       </c>
       <c r="M25">
-        <v>105909.00000000001</v>
+        <v>1779.0000000000007</v>
       </c>
       <c r="N25">
-        <v>105922.99630017641</v>
+        <v>1839.0122298883912</v>
       </c>
       <c r="O25">
-        <v>105936.99445002017</v>
+        <v>1901.048893580142</v>
       </c>
       <c r="P25">
-        <v>105950.99444977571</v>
+        <v>1965.1782826923416</v>
       </c>
       <c r="Q25">
-        <v>105964.99629968751</v>
+        <v>2031.4709925701416</v>
       </c>
       <c r="R25">
-        <v>105979.00000000007</v>
+        <v>2099.9999999999995</v>
       </c>
       <c r="S25">
-        <v>106529.25625615021</v>
+        <v>2151.9639090561727</v>
       </c>
       <c r="T25">
-        <v>107082.36951177609</v>
+        <v>2205.2136504192017</v>
       </c>
       <c r="U25">
-        <v>107638.35460077715</v>
+        <v>2259.7810416476846</v>
       </c>
       <c r="V25">
-        <v>108197.22643407235</v>
+        <v>2315.698687616753</v>
       </c>
       <c r="W25">
-        <v>108759.00000000003</v>
+        <v>2372.9999999999986</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -2283,67 +2292,67 @@
         <v>26</v>
       </c>
       <c r="C26">
-        <v>168478</v>
+        <v>3433</v>
       </c>
       <c r="D26">
-        <v>171564.24002051505</v>
+        <v>3460.7478070694078</v>
       </c>
       <c r="E26">
-        <v>174707.01488512979</v>
+        <v>3488.7198905143359</v>
       </c>
       <c r="F26">
-        <v>177907.36021925771</v>
+        <v>3516.9180630867791</v>
       </c>
       <c r="G26">
-        <v>181166.33061926754</v>
+        <v>3545.3441521906088</v>
       </c>
       <c r="H26">
-        <v>184485</v>
+        <v>3573.9999999999995</v>
       </c>
       <c r="I26">
-        <v>187604.50401055854</v>
+        <v>3601.959120508463</v>
       </c>
       <c r="J26">
-        <v>190776.7565116279</v>
+        <v>3630.1369630145773</v>
       </c>
       <c r="K26">
-        <v>194002.64944091413</v>
+        <v>3658.5352385633041</v>
       </c>
       <c r="L26">
-        <v>197283.08981812591</v>
+        <v>3687.1556715849742</v>
       </c>
       <c r="M26">
-        <v>200618.99999999991</v>
+        <v>3716.0000000000014</v>
       </c>
       <c r="N26">
-        <v>203755.38901361113</v>
+        <v>3750.7441882246976</v>
       </c>
       <c r="O26">
-        <v>206940.81095054807</v>
+        <v>3785.8132307592427</v>
       </c>
       <c r="P26">
-        <v>210176.03236992049</v>
+        <v>3821.2101649554352</v>
       </c>
       <c r="Q26">
-        <v>213461.83181488531</v>
+        <v>3856.9380565639767</v>
       </c>
       <c r="R26">
-        <v>216798.99999999994</v>
+        <v>3892.9999999999991</v>
       </c>
       <c r="S26">
-        <v>219937.03333221166</v>
+        <v>3930.0866256178251</v>
       </c>
       <c r="T26">
-        <v>223120.48778349708</v>
+        <v>3967.5265566041876</v>
       </c>
       <c r="U26">
-        <v>226350.0207968594</v>
+        <v>4005.3231587191526</v>
       </c>
       <c r="V26">
-        <v>229626.29933138838</v>
+        <v>4043.4798297866641</v>
       </c>
       <c r="W26">
-        <v>232949.99999999988</v>
+        <v>4082.0000000000023</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -2354,67 +2363,67 @@
         <v>27</v>
       </c>
       <c r="C27">
-        <v>108508</v>
+        <v>3030</v>
       </c>
       <c r="D27">
-        <v>109593.46467460811</v>
+        <v>3032.3962070292396</v>
       </c>
       <c r="E27">
-        <v>110689.7878440721</v>
+        <v>3034.7943090446597</v>
       </c>
       <c r="F27">
-        <v>111797.07813183527</v>
+        <v>3037.1943075448676</v>
       </c>
       <c r="G27">
-        <v>112915.44524796044</v>
+        <v>3039.5962040296549</v>
       </c>
       <c r="H27">
-        <v>114044.99999999999</v>
+        <v>3042</v>
       </c>
       <c r="I27">
-        <v>115158.25272390351</v>
+        <v>3044.3962219563464</v>
       </c>
       <c r="J27">
-        <v>116282.37248824965</v>
+        <v>3046.794331447099</v>
       </c>
       <c r="K27">
-        <v>117417.46537188775</v>
+        <v>3049.1943299590926</v>
       </c>
       <c r="L27">
-        <v>118563.63848915814</v>
+        <v>3051.5962189803336</v>
       </c>
       <c r="M27">
-        <v>119721.00000000006</v>
+        <v>3053.9999999999995</v>
       </c>
       <c r="N27">
-        <v>120764.6451336941</v>
+        <v>3055.598326140283</v>
       </c>
       <c r="O27">
-        <v>121817.38804609938</v>
+        <v>3057.1974887725273</v>
       </c>
       <c r="P27">
-        <v>122879.30804537801</v>
+        <v>3058.7974883345155</v>
       </c>
       <c r="Q27">
-        <v>123950.48513104599</v>
+        <v>3060.3983252642593</v>
       </c>
       <c r="R27">
-        <v>125030.99999999996</v>
+        <v>3061.9999999999986</v>
       </c>
       <c r="S27">
-        <v>125899.84064731625</v>
+        <v>3063.9973924364081</v>
       </c>
       <c r="T27">
-        <v>126774.71886987727</v>
+        <v>3065.9960878044117</v>
       </c>
       <c r="U27">
-        <v>127655.67662280446</v>
+        <v>3067.9960869539341</v>
       </c>
       <c r="V27">
-        <v>128542.75615276545</v>
+        <v>3069.9973907354533</v>
       </c>
       <c r="W27">
-        <v>129436</v>
+        <v>3072.0000000000018</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -2425,67 +2434,280 @@
         <v>28</v>
       </c>
       <c r="C28">
-        <v>165172</v>
+        <v>7531</v>
       </c>
       <c r="D28">
-        <v>165137.78582850515</v>
+        <v>7868.385652669177</v>
       </c>
       <c r="E28">
-        <v>165103.57874422564</v>
+        <v>8220.8860415788276</v>
       </c>
       <c r="F28">
-        <v>165069.37874569339</v>
+        <v>8589.1783005958241</v>
       </c>
       <c r="G28">
-        <v>165035.18583144067</v>
+        <v>8973.9698989012886</v>
       </c>
       <c r="H28">
-        <v>165001</v>
+        <v>9375.9999999999945</v>
       </c>
       <c r="I28">
-        <v>165001</v>
+        <v>9647.2452575636398</v>
       </c>
       <c r="J28">
-        <v>165001</v>
+        <v>9926.3375703481379</v>
       </c>
       <c r="K28">
-        <v>165001</v>
+        <v>10213.503951633624</v>
       </c>
       <c r="L28">
-        <v>165001</v>
+        <v>10508.97798213577</v>
       </c>
       <c r="M28">
-        <v>165001</v>
+        <v>10813.000000000002</v>
       </c>
       <c r="N28">
-        <v>165001</v>
+        <v>11011.943524139369</v>
       </c>
       <c r="O28">
-        <v>165001</v>
+        <v>11214.547320709795</v>
       </c>
       <c r="P28">
-        <v>165001</v>
+        <v>11420.878733417621</v>
       </c>
       <c r="Q28">
-        <v>165001</v>
+        <v>11631.006344995767</v>
       </c>
       <c r="R28">
-        <v>165001</v>
+        <v>11845.000000000005</v>
       </c>
       <c r="S28">
-        <v>165001</v>
+        <v>11996.285842379684</v>
       </c>
       <c r="T28">
-        <v>165001</v>
+        <v>12149.503926726826</v>
       </c>
       <c r="U28">
-        <v>165001</v>
+        <v>12304.678931880911</v>
       </c>
       <c r="V28">
-        <v>165001</v>
+        <v>12461.835851882697</v>
       </c>
       <c r="W28">
-        <v>165001</v>
+        <v>12620.999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29">
+        <v>26520</v>
+      </c>
+      <c r="D29">
+        <v>25834.46231657741</v>
+      </c>
+      <c r="E29">
+        <v>25166.645670688467</v>
+      </c>
+      <c r="F29">
+        <v>24516.091976397329</v>
+      </c>
+      <c r="G29">
+        <v>23882.354989215029</v>
+      </c>
+      <c r="H29">
+        <v>23265.000000000004</v>
+      </c>
+      <c r="I29">
+        <v>23058.776280677568</v>
+      </c>
+      <c r="J29">
+        <v>22854.380552862171</v>
+      </c>
+      <c r="K29">
+        <v>22651.796613020284</v>
+      </c>
+      <c r="L29">
+        <v>22451.008401248422</v>
+      </c>
+      <c r="M29">
+        <v>22251.999999999996</v>
+      </c>
+      <c r="N29">
+        <v>22192.684617235784</v>
+      </c>
+      <c r="O29">
+        <v>22133.527346759562</v>
+      </c>
+      <c r="P29">
+        <v>22074.527767104013</v>
+      </c>
+      <c r="Q29">
+        <v>22015.685457925283</v>
+      </c>
+      <c r="R29">
+        <v>21957</v>
+      </c>
+      <c r="S29">
+        <v>21968.787337438378</v>
+      </c>
+      <c r="T29">
+        <v>21980.581002759613</v>
+      </c>
+      <c r="U29">
+        <v>21992.380999360747</v>
+      </c>
+      <c r="V29">
+        <v>22004.187330640649</v>
+      </c>
+      <c r="W29">
+        <v>22016.000000000011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30">
+        <v>18046</v>
+      </c>
+      <c r="D30">
+        <v>18588.222219199528</v>
+      </c>
+      <c r="E30">
+        <v>19146.736410857979</v>
+      </c>
+      <c r="F30">
+        <v>19722.032094506645</v>
+      </c>
+      <c r="G30">
+        <v>20314.613498108982</v>
+      </c>
+      <c r="H30">
+        <v>20925.000000000004</v>
+      </c>
+      <c r="I30">
+        <v>21274.339314377801</v>
+      </c>
+      <c r="J30">
+        <v>21629.510789165161</v>
+      </c>
+      <c r="K30">
+        <v>21990.611791287705</v>
+      </c>
+      <c r="L30">
+        <v>22357.741313195322</v>
+      </c>
+      <c r="M30">
+        <v>22731.000000000004</v>
+      </c>
+      <c r="N30">
+        <v>23003.202255525885</v>
+      </c>
+      <c r="O30">
+        <v>23278.664115464831</v>
+      </c>
+      <c r="P30">
+        <v>23557.42461336897</v>
+      </c>
+      <c r="Q30">
+        <v>23839.523250214686</v>
+      </c>
+      <c r="R30">
+        <v>24125.000000000007</v>
+      </c>
+      <c r="S30">
+        <v>24342.637687385974</v>
+      </c>
+      <c r="T30">
+        <v>24562.238739040164</v>
+      </c>
+      <c r="U30">
+        <v>24783.820866965008</v>
+      </c>
+      <c r="V30">
+        <v>25007.40194294737</v>
+      </c>
+      <c r="W30">
+        <v>25232.999999999993</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31">
+        <v>68664</v>
+      </c>
+      <c r="D31">
+        <v>68635.977136185596</v>
+      </c>
+      <c r="E31">
+        <v>68607.965708944888</v>
+      </c>
+      <c r="F31">
+        <v>68579.965713610436</v>
+      </c>
+      <c r="G31">
+        <v>68551.977145516692</v>
+      </c>
+      <c r="H31">
+        <v>68524.000000000015</v>
+      </c>
+      <c r="I31">
+        <v>68368.89946330736</v>
+      </c>
+      <c r="J31">
+        <v>68214.149988673016</v>
+      </c>
+      <c r="K31">
+        <v>68059.750781486116</v>
+      </c>
+      <c r="L31">
+        <v>67905.701048934381</v>
+      </c>
+      <c r="M31">
+        <v>67752</v>
+      </c>
+      <c r="N31">
+        <v>67621.296681039137</v>
+      </c>
+      <c r="O31">
+        <v>67490.845507514387</v>
+      </c>
+      <c r="P31">
+        <v>67360.645993001061</v>
+      </c>
+      <c r="Q31">
+        <v>67230.697652012852</v>
+      </c>
+      <c r="R31">
+        <v>67101.000000000029</v>
+      </c>
+      <c r="S31">
+        <v>67009.148883412956</v>
+      </c>
+      <c r="T31">
+        <v>66917.423497107404</v>
+      </c>
+      <c r="U31">
+        <v>66825.823668977609</v>
+      </c>
+      <c r="V31">
+        <v>66734.349227153434</v>
+      </c>
+      <c r="W31">
+        <v>66642.999999999985</v>
       </c>
     </row>
   </sheetData>
